--- a/Config/Translation_degreeOfEstablishment.xlsx
+++ b/Config/Translation_degreeOfEstablishment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhD\1. Data paper\SInAS-dataset_final_v2\SInAS-workflow_update\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhD\1. Data paper\SInAS-dataset_final_v5 - 3.2\SInAS-workflow_update\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EF2A65-B45B-48C2-B5CC-79E16A11B5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CCEFCA-983E-46C9-9E51-CC2A2225ED4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>origTerm</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>widespreadInvasive</t>
+  </si>
+  <si>
+    <t>Introduced but not established</t>
   </si>
 </sst>
 </file>
@@ -448,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1025" width="11.33203125"/>
@@ -548,6 +551,14 @@
       </c>
       <c r="B12" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
